--- a/lekcja02/ZAD_2.xlsx
+++ b/lekcja02/ZAD_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\OneDrive\Dokumenty\GitHub\Programowanie-liniowe-i-optymalizacja\lekcja02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449D2537-32A7-44CE-8C06-B12B091B10BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A17DAC2-0B7B-4387-B665-F06CD662417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
